--- a/money-leak-finder/money-leak-finder-TEMPLATE.xlsx
+++ b/money-leak-finder/money-leak-finder-TEMPLATE.xlsx
@@ -682,7 +682,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Template by Automated Workflow LLC · automatedworkflowllc.com</t>
+          <t>Template by Automated Workflow · automatedworkflowllc.com</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>Template by Automated Workflow LLC · automatedworkflowllc.com</t>
+          <t>Template by Automated Workflow · automatedworkflowllc.com</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>Template by Automated Workflow LLC · automatedworkflowllc.com</t>
+          <t>Template by Automated Workflow · automatedworkflowllc.com</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Template by Automated Workflow LLC · automatedworkflowllc.com</t>
+          <t>Template by Automated Workflow · automatedworkflowllc.com</t>
         </is>
       </c>
     </row>
